--- a/docs/requirements-v1.01.xlsx
+++ b/docs/requirements-v1.01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5497E84E-D399-47F3-8C4F-F25A2A0D0F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4B848C-A219-4720-AE6E-E4E92F44D121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="14610" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="14610" windowHeight="7845" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -533,15 +533,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・モーニングブリーフの時間割(timetable.md)を直接読む。時間割を直すのはこのファイル1か所だけ。公開リポジトリには入れない
-・時間割の科目を、大学の入れ物として登録する
-・トップ画面に今日の授業を出す
-・読めなかったときは、画面に「時間割を読めませんでした」と出す
-・学期の入れ替えは自動にしない。学期が終わったら、自分が Claude に新しい時間割を説明し、Claude が時間割の書き換えと、終わった授業の入れ物の終了を行う。そのとき Claude は、何をどう変えたか(変更の仕方)を説明する
-・頼み忘れを防ぐため、学期の終わりが近づいたら、2段目のお知らせに「※学期が終わります。時間割の入れ替えを Claude に頼む」と米印つきで出す(案:学期の終わりの1週間前から)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>開いてから2秒以内(Claude の案)に、今日・今週のやることが出る。git・メール・カレンダーの読み込みは含めない。画面を先に出し、読み込みは裏で続け、読み込み中は2段目のお知らせに「読み込み中」と出す</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -646,18 +637,6 @@
     <t>要件定義 点検の差4・Google カレンダーのような機能を足したい・追加35〜40</t>
   </si>
   <si>
-    <t>・入れ物の種類「就活」で、企業ごとに入れ物を1つ作る(エントリーしたときに自分で作る)
-・ES の締切は、その企業の入れ物のタスクになる。面接日など日時が決まったものは、その企業の入れ物のスケジュール(F19)になる
-・企業からの連絡(個人の Gmail)を取り込む。読み方は Google の公式の連携(API)。最初に一度、Google の画面で許可する。許可の鍵は PC の中にだけ置き、公開リポジトリに入れない
-・企業の入れ物に、その企業のメールアドレス(@ から後ろ)を登録できる。差出人が一致したメールと、件名や本文に企業の入れ物の名前が入っているメール(就活サイト経由のもの)を、その企業の入れ物に振り分ける
-・振り分けを間違えたものは自分で入れ物を選び直せる。選び直した結果を覚える(F9 と同じ仕組み)
-・企業からの連絡は、F9 と同じ「連絡」の画面に「企業」として出す
-・Gmail は、アプリの起動時と10分ごと(Claude の案)に読む(F9 と同じ)
-・読めなかったとき(許可切れなど)は推測で埋めず、画面に「Gmail を読めませんでした」と出す
-・企業の入れ物に振り分けたメールに締切が書いてあれば、確認なしで自動でタスクに、面接日などの日時があれば自動でスケジュールにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない(F9 と同じ)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>済:企業からのメールをどう見分けるか → アドレスと企業名の両方で見分け、外れたら選び直し、覚える
 済:Gmail をどう読むか → Google の公式の連携(API)。F12・F13 のカレンダーと同じ許可を使う
 済(点検で追加):いつ読むか、読めなかったとき、締切や面接日の扱い → 3つとも F9 と同じ</t>
@@ -678,12 +657,6 @@
     <t>アルバイトの面接のメールを Gmail から拾い、スケジュールに入れる</t>
   </si>
   <si>
-    <t>・応募したバイト先の名前とメールアドレス(@ から後ろ)を、一覧に登録しておく。入れ物は作らない
-・Gmail の読み方・読めなかったときの扱いは F11 と同じ
-・登録したバイト先から届いたメールに面接の日時があれば、自動で入れ物なしのスケジュール(F19)にし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
-・バイト先からの連絡は、「連絡」の画面(F9)に「アルバイト」として出す</t>
-  </si>
-  <si>
     <t>済:どう見分けて、どこに入れるか → バイト先を一覧に登録して見分け、入れ物なしのスケジュールに入れる</t>
   </si>
   <si>
@@ -704,15 +677,6 @@
   </si>
   <si>
     <t>大学・就活・アルバイトと開発の一元管理</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>済:「手つかず」の決め方と日数 → 締切ありは締切の3日前に記録なし、締切なしは登録から3日間記録なし
-済:「長い」の時間 → 2時間
-済:アプリを閉じているときの通知 → 画面を閉じていても通知する(PC 起動時に自動で立ち上がる)
-・画面での知らせ(締切の前日・手つかず・2時間・着手日)と、F18 ③の「このタスクは終わった?」を、画面のどこに出すか
-・F14 と F18 ④(claude -p)が読み取れなかったときの出し方
-→ 基本設計で決める</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -831,19 +795,6 @@
 済:いつ読むか、Outlook が起動していないときの扱い → 起動時と10分ごと。閉じていれば裏で立ち上げる
 済(点検で追加):「その他」のメールから自動で入ったタスクの入れ物 → 未分類に入れて印をつける
 済(点検で追加):取り込んだ連絡をどこで見るか → 「連絡」の画面。トップは2段目に件数だけ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・一番上に、全体の進み具合のゲージを細く1本出す。そのすぐ下に、「トップに出す」を選んだ入れ物のゲージを出す(F6)
-・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」
-・2段目に出すものは次の9つ:①作業記録の再開の確認(F4)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F7・F9・F10・F11・F12・F19)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11・F20)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
-・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
-・その下に、今日の時間(F10・F12)を出す。今日の時間には、授業・面接など時刻の決まった予定だけを出し、タスクの締切は出さない(今日が締切のタスクは「今日」の欄にだけ出す)
-・その下に「今日」と「今週」に分けて、締切の近い順に並べる
-・締切のないタスクは、その下に「締切なし」としてまとめて出す
-・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら「先に並べる」設定の種類を先(初めは大学・就活) ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
-・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を種類ごとの色で分ける(F1)
-・「未分類」のタスクのラベルは灰色にする(F1)</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -970,14 +921,6 @@
   </si>
   <si>
     <t>1.00</t>
-  </si>
-  <si>
-    <t>新しく払うお金は0円。有料のサービスや API を新しく契約しない(今の Claude Code の契約は含めない。F9・F11・F14・F18・F20 はその範囲で動かす)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>Windows 11 の PC。次がそろっていること:Chrome/Outlook アプリ(クラシック版、大学のアカウントでサインイン済み)/Claude Code(ログイン済み。F9・F11・F14・F18・F20 で使う)/Google アカウントの許可(F11〜F13 で使う)/モーニングブリーフの時間割ファイル timetable.md(F10 で使う)</t>
-    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>・PC の Outlook アプリ(クラシック版)を読み取り専用で読む(モーニングブリーフと同じ方法)
@@ -1001,10 +944,72 @@
     <t>1.01</t>
   </si>
   <si>
-    <t>構想設計で決めたことを反映(締切の読み取りに Claude を使う:F9・F11・F20、非機能 C1・C4)</t>
-  </si>
-  <si>
     <t>ver.1.01</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・一番上に、全体の進み具合のゲージを細く1本出す。そのすぐ下に、「トップに出す」を選んだ入れ物のゲージを出す(F6)
+・その下は役割ごとに3段に分ける。1段目:記録中の作業(F4)。2段目:お知らせ(あるときだけ出す)。3段目:「期限切れ」
+・2段目に出すものは次の9つ:①作業記録の再開の確認(F4)②PC の電源が切れていた間の通知(F8)③学期の終わりの米印(F10)④読めなかった・つながらなかった(F7・F9・F10・F11・F12・F19。Claude の締切の読み取り F9・F11・F20 も含む)⑤読み込み中(非機能要件)⑥カレンダーに書かなかった予定(F13)⑦新しい連絡の件数(F9・F11・F20)⑧「終わっていそう」なタスクの件数(F18)⑨未分類の件数(F2)
+・「期限切れ」には、締切を過ぎたタスクを色を変えてまとめる。完了にするか締切を変えるまで残る
+・その下に、今日の時間(F10・F12)を出す。今日の時間には、授業・面接など時刻の決まった予定だけを出し、タスクの締切は出さない(今日が締切のタスクは「今日」の欄にだけ出す)
+・その下に「今日」と「今週」に分けて、締切の近い順に並べる
+・締切のないタスクは、その下に「締切なし」としてまとめて出す
+・同じ締切の日の中は、①時刻があるものは時刻順、時刻なしはその日の最後 ②同じなら「先に並べる」設定の種類を先(初めは大学・就活) ③さらに同じなら登録が古い順。「締切なし」の中は登録が古い順
+・各タスクに入れ物の名前のラベル(例:「卒論」「fx-practice」)をつけ、ラベルの色を種類ごとの色で分ける(F1)
+・「未分類」のタスクのラベルは灰色にする(F1)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>済:「手つかず」の決め方と日数 → 締切ありは締切の3日前に記録なし、締切なしは登録から3日間記録なし
+済:「長い」の時間 → 2時間
+済:アプリを閉じているときの通知 → 画面を閉じていても通知する(PC 起動時に自動で立ち上がる)
+・画面での知らせ(締切の前日・手つかず・2時間・着手日)と、F18 ③の「このタスクは終わった?」を、画面のどこに出すか
+・F9・F11・F14・F18 ④・F20(claude -p)が読み取れなかったときの出し方
+→ 基本設計で決める</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・モーニングブリーフの時間割(timetable.md)を直接読む。時間割を直すのはこのファイル1か所だけ。公開リポジトリには入れない
+・時間割の科目を、大学の入れ物として登録する
+・トップ画面に今日の授業を出す
+・読めなかったときは、画面に「時間割を読めませんでした」と出す
+・学期の入れ替えは自動にしない。学期が終わったら、自分が Claude に新しい時間割を説明し、Claude が時間割の書き換えと、終わった授業の入れ物の終了を行う。そのとき Claude は、何をどう変えたか(変更の仕方)を説明する
+・頼み忘れを防ぐため、学期の終わりが近づいたら、2段目のお知らせに「※学期が終わります。時間割の入れ替えを Claude に頼む」と米印つきで出す(案:学期の終わりの1週間前から)
+・時間割は、アプリの起動時と10分ごと(Claude の案)に読む</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・入れ物の種類「就活」で、企業ごとに入れ物を1つ作る(エントリーしたときに自分で作る)
+・ES の締切は、その企業の入れ物のタスクになる。面接日など日時が決まったものは、その企業の入れ物のスケジュール(F19)になる
+・企業からの連絡(個人の Gmail)を取り込む。読み方は Google の公式の連携(API)。最初に一度、Google の画面で許可する。許可の鍵は PC の中にだけ置き、公開リポジトリに入れない
+・企業の入れ物に、その企業のメールアドレス(@ から後ろ)を登録できる。差出人が一致したメールと、件名や本文に企業の入れ物の名前が入っているメール(就活サイト経由のもの)を、その企業の入れ物に振り分ける
+・振り分けを間違えたものは自分で入れ物を選び直せる。選び直した結果を覚える(F9 と同じ仕組み)
+・企業からの連絡は、F9 と同じ「連絡」の画面に「企業」として出す
+・Gmail は、アプリの起動時と10分ごと(Claude の案)に読む(F9 と同じ)
+・読めなかったとき(許可切れなど)は推測で埋めず、画面に「Gmail を読めませんでした」と出す
+・企業の入れ物に振り分けたメールに締切が書いてあれば、確認なしで自動でタスクに、面接日などの日時があれば自動でスケジュールにし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない(F9 と同じ)
+・締切・面接日の読み取りは F9 と同じ(決まった書き方で見つからないときだけ Claude に読ませ、「Claude が読み取った」印をつける)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・応募したバイト先の名前とメールアドレス(@ から後ろ)を、一覧に登録しておく。入れ物は作らない
+・Gmail の読み方・読めなかったときの扱いは F11 と同じ
+・登録したバイト先から届いたメールに面接の日時があれば、自動で入れ物なしのスケジュール(F19)にし、「メールから自動で入った」印をつける。間違っていたら1回の操作で消せ、消したものは次に読んだときに復活しない
+・バイト先からの連絡は、「連絡」の画面(F9)に「アルバイト」として出す
+・面接日の読み取りは F9 と同じ(決まった書き方で見つからないときだけ Claude に読ませ、「Claude が読み取った」印をつける)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>新しく払うお金は0円。有料のサービスや API を新しく契約しない(今の Claude Code の契約は含めない。F9・F10・F11・F14・F18・F20 はその範囲で動かす)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Windows 11 の PC。次がそろっていること:Chrome/Outlook アプリ(クラシック版、大学のアカウントでサインイン済み)/Claude Code(ログイン済み。F9・F10・F11・F14・F18・F20 で使う)/Google アカウントの許可(F11〜F13 で使う)/モーニングブリーフの時間割ファイル timetable.md(F10 で使う)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>構想設計で決めたことを反映(締切・面接日の読み取りに Claude を使う:F9・F11・F20、学期の入れ替えで Claude を使う:F10、時間割を読む時期:F10、非機能 C1・C4)</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1624,7 +1629,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
@@ -1647,7 +1652,7 @@
     </row>
     <row r="13" spans="1:10" ht="37.5">
       <c r="F13" s="31" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>129</v>
@@ -1733,7 +1738,7 @@
     </row>
     <row r="2" spans="1:9" ht="148.5">
       <c r="A2" s="16" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5">
@@ -1811,10 +1816,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="13">
@@ -1825,15 +1830,15 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="33">
+    <row r="9" spans="1:9" ht="49.5">
       <c r="A9" s="4">
         <v>3</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="30">
@@ -2061,7 +2066,7 @@
     </row>
     <row r="2" spans="1:3" ht="66">
       <c r="A2" s="16" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5">
@@ -2086,7 +2091,7 @@
         <v>108</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="54">
@@ -2144,7 +2149,7 @@
     </row>
     <row r="2" spans="1:7" ht="66">
       <c r="A2" s="16" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5">
@@ -2183,19 +2188,19 @@
         <v>42</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="280.5">
@@ -2207,7 +2212,7 @@
         <v>45</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>43</v>
@@ -2219,22 +2224,22 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="396">
+    <row r="8" spans="1:7" ht="409.5">
       <c r="A8" s="8"/>
       <c r="B8" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>203</v>
+        <v>189</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>215</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>93</v>
@@ -2288,16 +2293,16 @@
         <v>51</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>96</v>
@@ -2309,10 +2314,10 @@
         <v>52</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>43</v>
@@ -2333,13 +2338,13 @@
         <v>54</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>186</v>
+      <c r="F13" s="28" t="s">
+        <v>216</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>98</v>
@@ -2354,19 +2359,19 @@
         <v>106</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="214.5">
+    <row r="15" spans="1:7" ht="231">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
         <v>75</v>
@@ -2374,8 +2379,8 @@
       <c r="C15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>147</v>
+      <c r="D15" s="28" t="s">
+        <v>217</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>43</v>
@@ -2393,16 +2398,16 @@
         <v>130</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>173</v>
+        <v>190</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>218</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>131</v>
@@ -2417,13 +2422,13 @@
         <v>133</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G17" s="15" t="s">
         <v>134</v>
@@ -2438,13 +2443,13 @@
         <v>136</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G18" s="15" t="s">
         <v>137</v>
@@ -2477,16 +2482,16 @@
         <v>143</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>144</v>
@@ -2495,106 +2500,106 @@
     <row r="21" spans="1:7" ht="94.5">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="E21" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" s="9" t="s">
+      <c r="G21" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="121.5">
       <c r="A22" s="11"/>
       <c r="B22" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="G22" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="283.5">
       <c r="A23" s="11"/>
       <c r="B23" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="E23" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G23" s="11" t="s">
         <v>165</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="409.5">
       <c r="A24" s="11"/>
       <c r="B24" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>170</v>
-      </c>
       <c r="D24" s="11" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>43</v>
       </c>
       <c r="F24" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G24" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="121.5">
+    </row>
+    <row r="25" spans="1:7" ht="162">
       <c r="A25" s="11"/>
       <c r="B25" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="G25" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2619,7 +2624,7 @@
     </row>
     <row r="2" spans="1:1" ht="99">
       <c r="A2" s="16" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="16.5">
@@ -2660,7 +2665,7 @@
     </row>
     <row r="2" spans="1:4" ht="66">
       <c r="A2" s="16" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5">
@@ -2690,7 +2695,7 @@
         <v>56</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>113</v>
@@ -2718,7 +2723,7 @@
         <v>61</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>62</v>
@@ -2732,7 +2737,7 @@
         <v>63</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>64</v>
@@ -2760,10 +2765,10 @@
         <v>70</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33">
@@ -2872,7 +2877,7 @@
         <v>81</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>71</v>
@@ -2914,7 +2919,7 @@
         <v>86</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>71</v>
@@ -2956,10 +2961,10 @@
         <v>110</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27">
@@ -2970,7 +2975,7 @@
         <v>111</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>112</v>
@@ -2981,13 +2986,13 @@
         <v>65</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
